--- a/Smart_Parking_Platform_Project_Plan.xlsx
+++ b/Smart_Parking_Platform_Project_Plan.xlsx
@@ -82,67 +82,67 @@
     <t>Formulate 15 System Use Cases &amp; Functional MatriX</t>
   </si>
   <si>
+    <t>Homework 2 Submission</t>
+  </si>
+  <si>
+    <t>Due Sept. 17th by 11:59 PM</t>
+  </si>
+  <si>
+    <t>Build Hierarchical Work Breakdown Struture (WBS) Blocks</t>
+  </si>
+  <si>
+    <t>Homework 3 Submission</t>
+  </si>
+  <si>
+    <t>Due Sept. 24th. Decomposing system components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply Software Workload Estimations (Story Points &amp; COCOMO Models) </t>
+  </si>
+  <si>
+    <t>Homework 4 Submission</t>
+  </si>
+  <si>
+    <t>Due Oct. 1st. Modeling framework rules.</t>
+  </si>
+  <si>
+    <t>Design UI/UX Wireframe Dashboard Views (Web &amp; Mobile Formats)</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Homework 5 Submission</t>
+  </si>
+  <si>
+    <t>Due Oct. 8. User experience blueprint mapping</t>
+  </si>
+  <si>
+    <t>Navigation Map Overlay &amp; Payment Processing Gateway APIs</t>
+  </si>
+  <si>
+    <t>Homework 6 Submission</t>
+  </si>
+  <si>
+    <t>Due Oct 15th. Third-party dependency validation.</t>
+  </si>
+  <si>
+    <t>Milestone: Complete Midterm Exam Evaluation Review</t>
+  </si>
+  <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>Homework 2 Submission</t>
-  </si>
-  <si>
-    <t>Due Sept. 17th by 11:59 PM</t>
-  </si>
-  <si>
-    <t>Build Hierarchical Work Breakdown Struture (WBS) Blocks</t>
+    <t>Classroom Evaluation Milestone</t>
+  </si>
+  <si>
+    <t>Midterm evaluation milestone on Oct 16th.</t>
+  </si>
+  <si>
+    <t>Develop Profile Authorization &amp; Secure Sign In Portals (FRI)</t>
   </si>
   <si>
     <t>Not started</t>
-  </si>
-  <si>
-    <t>Homework 3 Submission</t>
-  </si>
-  <si>
-    <t>Due Sept. 24th. Decomposing system components</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply Software Workload Estimations (Story Points &amp; COCOMO Models) </t>
-  </si>
-  <si>
-    <t>Homework 4 Submission</t>
-  </si>
-  <si>
-    <t>Due Oct. 1st. Modeling framework rules.</t>
-  </si>
-  <si>
-    <t>Design UI/UX Wireframe Dashboard Views (Web &amp; Mobile Formats)</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Homework 5 Submission</t>
-  </si>
-  <si>
-    <t>Due Oct. 8. User experience blueprint mapping</t>
-  </si>
-  <si>
-    <t>Navigation Map Overlay &amp; Payment Processing Gateway APIs</t>
-  </si>
-  <si>
-    <t>Homework 6 Submission</t>
-  </si>
-  <si>
-    <t>Due Oct 15th. Third-party dependency validation.</t>
-  </si>
-  <si>
-    <t>Milestone: Complete Midterm Exam Evaluation Review</t>
-  </si>
-  <si>
-    <t>Classroom Evaluation Milestone</t>
-  </si>
-  <si>
-    <t>Midterm evaluation milestone on Oct 16th.</t>
-  </si>
-  <si>
-    <t>Develop Profile Authorization &amp; Secure Sign In Portals (FRI)</t>
   </si>
   <si>
     <t>Homework 7 Submission</t>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E5" s="6">
         <v>46276.0</v>
@@ -718,16 +718,16 @@
         <v>46282.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>16</v>
@@ -736,7 +736,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E6" s="6">
         <v>46283.0</v>
@@ -745,16 +745,16 @@
         <v>46289.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>16</v>
@@ -763,7 +763,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E7" s="6">
         <v>46290.0</v>
@@ -772,25 +772,25 @@
         <v>46296.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E8" s="6">
         <v>46297.0</v>
@@ -799,16 +799,16 @@
         <v>46303.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>16</v>
@@ -817,7 +817,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E9" s="6">
         <v>46304.0</v>
@@ -826,16 +826,16 @@
         <v>46310.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
@@ -844,7 +844,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E10" s="6">
         <v>46311.0</v>
@@ -853,16 +853,16 @@
         <v>46311.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>16</v>
@@ -871,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E11" s="6">
         <v>46312.0</v>
@@ -898,7 +898,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E12" s="6">
         <v>46325.0</v>
@@ -925,7 +925,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6">
         <v>46301.0</v>
@@ -946,13 +946,13 @@
         <v>52</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E14" s="6">
         <v>46339.0</v>
@@ -979,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E15" s="6">
         <v>46346.0</v>
@@ -988,7 +988,7 @@
         <v>46346.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="2" t="s">
@@ -1006,7 +1006,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E16" s="6">
         <v>46347.0</v>
@@ -1033,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E17" s="6">
         <v>46354.0</v>
@@ -1060,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E18" s="6">
         <v>46360.0</v>
